--- a/excel/loss_functions.xlsx
+++ b/excel/loss_functions.xlsx
@@ -1,50 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SG\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\조근하\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE52AF9-DAC5-41D1-8B5A-F57A71E5C782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAF2F11-BCEE-4311-B4E7-4F078D9BD8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{064F2A64-9CD9-400C-9F24-93DDEFEC9914}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{064F2A64-9CD9-400C-9F24-93DDEFEC9914}"/>
   </bookViews>
   <sheets>
-    <sheet name="Log-Loss" sheetId="1" r:id="rId1"/>
-    <sheet name="Cross-Entropy" sheetId="2" r:id="rId2"/>
+    <sheet name="loss" sheetId="3" r:id="rId1"/>
+    <sheet name="Log-Loss" sheetId="1" r:id="rId2"/>
+    <sheet name="Cross-Entropy" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -59,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
   <si>
     <t>y*log(p)</t>
   </si>
@@ -166,18 +156,65 @@
     <t>Sum(softmax)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>P(y=1)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>confusion
+matrix</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(y=0)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H(P,Q)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>logloss</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H(P, Q)
+inner product</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>y(actual)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dog</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fish</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Loss</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="178" formatCode="#,##0_ "/>
+    <numFmt numFmtId="184" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,8 +306,15 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="D2Coding"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,8 +333,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -477,6 +533,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -486,7 +577,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -571,6 +662,78 @@
     <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="13" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="14" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -583,32 +746,14 @@
     <xf numFmtId="176" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="13" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="14" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -616,59 +761,98 @@
     <xf numFmtId="176" fontId="8" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="13" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="14" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="19" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="20" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -689,6 +873,111 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>243460</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>266854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>393583</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>233592</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02D332E0-68C0-4F0A-9C52-AB0AA2C88518}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{BEBA8EAE-BF5A-486C-A8C5-ECC9F3942E4B}">
+              <a14:imgProps xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a14:imgLayer r:embed="rId2">
+                  <a14:imgEffect>
+                    <a14:colorTemperature colorTemp="7200"/>
+                  </a14:imgEffect>
+                </a14:imgLayer>
+              </a14:imgProps>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13949434" y="4116959"/>
+          <a:ext cx="3518965" cy="919238"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>312617</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>29308</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1036</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>194072</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61D6125C-9DFD-458F-9BB9-600BEA20B2ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12133386" y="1709616"/>
+          <a:ext cx="4389990" cy="457842"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -849,7 +1138,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1350,44 +1639,1218 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C67523B7-4949-4BD9-8C88-0BCD9DF7A289}">
+  <dimension ref="A1:N28"/>
+  <sheetFormatPr defaultRowHeight="23.4" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="3" width="9.19921875" style="61" customWidth="1"/>
+    <col min="4" max="4" width="17" style="61" customWidth="1"/>
+    <col min="5" max="7" width="17.19921875" style="61" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" style="63" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5" style="61" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.8984375" style="61" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.19921875" style="61" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.296875" style="61" customWidth="1"/>
+    <col min="13" max="13" width="23.19921875" style="61" customWidth="1"/>
+    <col min="14" max="14" width="12.19921875" style="61" customWidth="1"/>
+    <col min="15" max="16384" width="8.796875" style="61"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H1" s="61"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="72" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="72"/>
+    </row>
+    <row r="2" spans="1:14" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="B2" s="75"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="68"/>
+      <c r="H2" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="72"/>
+      <c r="K2" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B3" s="64">
+        <v>0</v>
+      </c>
+      <c r="C3" s="64">
+        <f>1-B3</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="64">
+        <f>B3</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="7">
+        <f ca="1">RAND()</f>
+        <v>0.44164730227502536</v>
+      </c>
+      <c r="F3" s="7">
+        <f ca="1">1-E3</f>
+        <v>0.55835269772497464</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="66">
+        <f ca="1">IF(E3&gt;= 0.5, TRUE, FALSE)*1</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="63" t="str">
+        <f ca="1">IF(AND(D3=1, H3=1), "TP",
+ IF(AND(D3=0, H3=0), "TN",
+  IF(AND(D3=0, H3=1), "FP",
+   IF(AND(D3=1, H3=0), "FN", ""))))</f>
+        <v>TN</v>
+      </c>
+      <c r="J3" s="67">
+        <f ca="1">-SUMPRODUCT(B3:C3, LN(E3:F3))</f>
+        <v>0.58276444150001172</v>
+      </c>
+      <c r="K3" s="67">
+        <f ca="1">-D3*LN(E3)</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="67">
+        <f ca="1">-C3*LN(F3)</f>
+        <v>0.58276444150001172</v>
+      </c>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B4" s="64">
+        <v>1</v>
+      </c>
+      <c r="C4" s="64">
+        <f t="shared" ref="C4:C12" si="0">1-B4</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="64">
+        <f t="shared" ref="D4:D10" si="1">B4</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" ref="E4:E12" ca="1" si="2">RAND()</f>
+        <v>0.61381296043493216</v>
+      </c>
+      <c r="F4" s="7">
+        <f ca="1">1-E4</f>
+        <v>0.38618703956506784</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="66">
+        <f ca="1">IF(E4&gt;= 0.5, TRUE, FALSE)*1</f>
+        <v>1</v>
+      </c>
+      <c r="I4" s="63" t="str">
+        <f ca="1">IF(AND(D4=1, H4=1), "TP",
+ IF(AND(D4=0, H4=0), "TN",
+  IF(AND(D4=0, H4=1), "FP",
+   IF(AND(D4=1, H4=0), "FN", ""))))</f>
+        <v>TP</v>
+      </c>
+      <c r="J4" s="67">
+        <f ca="1">-SUMPRODUCT(B4:C4, LN(E4:F4))</f>
+        <v>0.4880650219413305</v>
+      </c>
+      <c r="K4" s="67">
+        <f ca="1">-D4*LN(E4)</f>
+        <v>0.4880650219413305</v>
+      </c>
+      <c r="L4" s="67">
+        <f ca="1">-C4*LN(F4)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B5" s="64">
+        <v>0</v>
+      </c>
+      <c r="C5" s="64">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D5" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.729862224005428</v>
+      </c>
+      <c r="F5" s="7">
+        <f ca="1">1-E5</f>
+        <v>0.270137775994572</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="66">
+        <f ca="1">IF(E5&gt;= 0.5, TRUE, FALSE)*1</f>
+        <v>1</v>
+      </c>
+      <c r="I5" s="63" t="str">
+        <f ca="1">IF(AND(D5=1, H5=1), "TP",
+ IF(AND(D5=0, H5=0), "TN",
+  IF(AND(D5=0, H5=1), "FP",
+   IF(AND(D5=1, H5=0), "FN", ""))))</f>
+        <v>FP</v>
+      </c>
+      <c r="J5" s="67">
+        <f ca="1">-SUMPRODUCT(B5:C5, LN(E5:F5))</f>
+        <v>1.308823168671696</v>
+      </c>
+      <c r="K5" s="67">
+        <f ca="1">-D5*LN(E5)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="67">
+        <f ca="1">-C5*LN(F5)</f>
+        <v>1.308823168671696</v>
+      </c>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B6" s="64">
+        <v>1</v>
+      </c>
+      <c r="C6" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="64">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.85855467067292812</v>
+      </c>
+      <c r="F6" s="7">
+        <f ca="1">1-E6</f>
+        <v>0.14144532932707188</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="66">
+        <f ca="1">IF(E6&gt;= 0.5, TRUE, FALSE)*1</f>
+        <v>1</v>
+      </c>
+      <c r="I6" s="63" t="str">
+        <f ca="1">IF(AND(D6=1, H6=1), "TP",
+ IF(AND(D6=0, H6=0), "TN",
+  IF(AND(D6=0, H6=1), "FP",
+   IF(AND(D6=1, H6=0), "FN", ""))))</f>
+        <v>TP</v>
+      </c>
+      <c r="J6" s="67">
+        <f ca="1">-SUMPRODUCT(B6:C6, LN(E6:F6))</f>
+        <v>0.15250491904968144</v>
+      </c>
+      <c r="K6" s="67">
+        <f ca="1">-D6*LN(E6)</f>
+        <v>0.15250491904968144</v>
+      </c>
+      <c r="L6" s="67">
+        <f ca="1">-C6*LN(F6)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B7" s="64">
+        <v>0</v>
+      </c>
+      <c r="C7" s="64">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D7" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.9253285703084444</v>
+      </c>
+      <c r="F7" s="7">
+        <f ca="1">1-E7</f>
+        <v>7.4671429691555602E-2</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="66">
+        <f ca="1">IF(E7&gt;= 0.5, TRUE, FALSE)*1</f>
+        <v>1</v>
+      </c>
+      <c r="I7" s="63" t="str">
+        <f ca="1">IF(AND(D7=1, H7=1), "TP",
+ IF(AND(D7=0, H7=0), "TN",
+  IF(AND(D7=0, H7=1), "FP",
+   IF(AND(D7=1, H7=0), "FN", ""))))</f>
+        <v>FP</v>
+      </c>
+      <c r="J7" s="67">
+        <f ca="1">-SUMPRODUCT(B7:C7, LN(E7:F7))</f>
+        <v>2.5946577273178297</v>
+      </c>
+      <c r="K7" s="67">
+        <f ca="1">-D7*LN(E7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="67">
+        <f ca="1">-C7*LN(F7)</f>
+        <v>2.5946577273178297</v>
+      </c>
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B8" s="64">
+        <v>1</v>
+      </c>
+      <c r="C8" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="64">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.94588552689459038</v>
+      </c>
+      <c r="F8" s="7">
+        <f ca="1">1-E8</f>
+        <v>5.4114473105409622E-2</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="66">
+        <f ca="1">IF(E8&gt;= 0.5, TRUE, FALSE)*1</f>
+        <v>1</v>
+      </c>
+      <c r="I8" s="63" t="str">
+        <f ca="1">IF(AND(D8=1, H8=1), "TP",
+ IF(AND(D8=0, H8=0), "TN",
+  IF(AND(D8=0, H8=1), "FP",
+   IF(AND(D8=1, H8=0), "FN", ""))))</f>
+        <v>TP</v>
+      </c>
+      <c r="J8" s="67">
+        <f ca="1">-SUMPRODUCT(B8:C8, LN(E8:F8))</f>
+        <v>5.563372476326215E-2</v>
+      </c>
+      <c r="K8" s="67">
+        <f ca="1">-D8*LN(E8)</f>
+        <v>5.563372476326215E-2</v>
+      </c>
+      <c r="L8" s="67">
+        <f ca="1">-C8*LN(F8)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="63"/>
+      <c r="N8" s="63"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B9" s="64">
+        <v>0</v>
+      </c>
+      <c r="C9" s="64">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D9" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="7">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.79312906221382218</v>
+      </c>
+      <c r="F9" s="7">
+        <f ca="1">1-E9</f>
+        <v>0.20687093778617782</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="66">
+        <f ca="1">IF(E9&gt;= 0.5, TRUE, FALSE)*1</f>
+        <v>1</v>
+      </c>
+      <c r="I9" s="63" t="str">
+        <f ca="1">IF(AND(D9=1, H9=1), "TP",
+ IF(AND(D9=0, H9=0), "TN",
+  IF(AND(D9=0, H9=1), "FP",
+   IF(AND(D9=1, H9=0), "FN", ""))))</f>
+        <v>FP</v>
+      </c>
+      <c r="J9" s="67">
+        <f ca="1">-SUMPRODUCT(B9:C9, LN(E9:F9))</f>
+        <v>1.5756601691224987</v>
+      </c>
+      <c r="K9" s="67">
+        <f ca="1">-D9*LN(E9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="67">
+        <f ca="1">-C9*LN(F9)</f>
+        <v>1.5756601691224987</v>
+      </c>
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B10" s="64">
+        <v>1</v>
+      </c>
+      <c r="C10" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D10" s="64">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E10" s="7">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.62103674466760028</v>
+      </c>
+      <c r="F10" s="7">
+        <f ca="1">1-E10</f>
+        <v>0.37896325533239972</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="66">
+        <f ca="1">IF(E10&gt;= 0.5, TRUE, FALSE)*1</f>
+        <v>1</v>
+      </c>
+      <c r="I10" s="63" t="str">
+        <f ca="1">IF(AND(D10=1, H10=1), "TP",
+ IF(AND(D10=0, H10=0), "TN",
+  IF(AND(D10=0, H10=1), "FP",
+   IF(AND(D10=1, H10=0), "FN", ""))))</f>
+        <v>TP</v>
+      </c>
+      <c r="J10" s="67">
+        <f ca="1">-SUMPRODUCT(B10:C10, LN(E10:F10))</f>
+        <v>0.47636502864197666</v>
+      </c>
+      <c r="K10" s="67">
+        <f ca="1">-D10*LN(E10)</f>
+        <v>0.47636502864197666</v>
+      </c>
+      <c r="L10" s="67">
+        <f ca="1">-C10*LN(F10)</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="63"/>
+      <c r="N10" s="63"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B11" s="64">
+        <v>0</v>
+      </c>
+      <c r="C11" s="64">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D11" s="64">
+        <f t="shared" ref="D11:D12" si="3">B11</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.27628751630996817</v>
+      </c>
+      <c r="F11" s="7">
+        <f ca="1">1-E11</f>
+        <v>0.72371248369003183</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="66">
+        <f ca="1">IF(E11&gt;= 0.5, TRUE, FALSE)*1</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="63" t="str">
+        <f ca="1">IF(AND(D11=1, H11=1), "TP",
+ IF(AND(D11=0, H11=0), "TN",
+  IF(AND(D11=0, H11=1), "FP",
+   IF(AND(D11=1, H11=0), "FN", ""))))</f>
+        <v>TN</v>
+      </c>
+      <c r="J11" s="67">
+        <f ca="1">-SUMPRODUCT(B11:C11, LN(E11:F11))</f>
+        <v>0.32336108744532877</v>
+      </c>
+      <c r="K11" s="67">
+        <f ca="1">-D11*LN(E11)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="67">
+        <f ca="1">-C11*LN(F11)</f>
+        <v>0.32336108744532877</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B12" s="64">
+        <v>1</v>
+      </c>
+      <c r="C12" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D12" s="64">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E12" s="7">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.13009764777186539</v>
+      </c>
+      <c r="F12" s="7">
+        <f ca="1">1-E12</f>
+        <v>0.86990235222813461</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="66">
+        <f ca="1">IF(E12&gt;= 0.5, TRUE, FALSE)*1</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="63" t="str">
+        <f ca="1">IF(AND(D12=1, H12=1), "TP",
+ IF(AND(D12=0, H12=0), "TN",
+  IF(AND(D12=0, H12=1), "FP",
+   IF(AND(D12=1, H12=0), "FN", ""))))</f>
+        <v>FN</v>
+      </c>
+      <c r="J12" s="67">
+        <f ca="1">-SUMPRODUCT(B12:C12, LN(E12:F12))</f>
+        <v>2.039469973781888</v>
+      </c>
+      <c r="K12" s="67">
+        <f ca="1">-D12*LN(E12)</f>
+        <v>2.039469973781888</v>
+      </c>
+      <c r="L12" s="67">
+        <f ca="1">-C12*LN(F12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H13" s="61"/>
+      <c r="I13" s="63" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="67">
+        <f ca="1">SUM(J3:J12)</f>
+        <v>9.5973052622355031</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="H14" s="61"/>
+    </row>
+    <row r="15" spans="1:14" ht="24" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="N15" s="61" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="31.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="62"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="79" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="80"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="77" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="80"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" s="82" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="31.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="83" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="83" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="76" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="76" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="89" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="89" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="78"/>
+      <c r="I17" s="84" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="86" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="91"/>
+      <c r="M17" s="87"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A18" s="64">
+        <f t="shared" ref="A18:A27" ca="1" si="4">RANDBETWEEN(0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="B18" s="64">
+        <f t="shared" ref="B18:B27" ca="1" si="5">IF(A18 &gt; 0, 0, RANDBETWEEN(0,1))</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="64">
+        <f t="shared" ref="C18" ca="1" si="6">IF(SUM(A18:B18) &gt;0, 0, RANDBETWEEN(0,1))</f>
+        <v>1</v>
+      </c>
+      <c r="D18" s="64" t="str">
+        <f ca="1">IF(A18=1, "Cat", IF(B18=1, "Dog", "Fish"))</f>
+        <v>Fish</v>
+      </c>
+      <c r="E18" s="3">
+        <f ca="1">RAND()</f>
+        <v>0.57228920052664556</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" ref="F18:G18" ca="1" si="7">RAND()</f>
+        <v>0.1969476105207183</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.72476879295514929</v>
+      </c>
+      <c r="H18" s="65" t="str">
+        <f ca="1">_xlfn.IFS(E18=MAX(E18:G18), "Cat", F18=MAX(E18:G18), "Dog", TRUE, "Fish")</f>
+        <v>Fish</v>
+      </c>
+      <c r="I18" s="3">
+        <f ca="1">EXP(E18)/SUM(EXP($E18)+EXP($F18)+EXP($G18))</f>
+        <v>0.35065901657106208</v>
+      </c>
+      <c r="J18" s="3">
+        <f ca="1">EXP(F18)/SUM(EXP($E18)+EXP($F18)+EXP($G18))</f>
+        <v>0.24092187203954663</v>
+      </c>
+      <c r="K18" s="3">
+        <f ca="1">EXP(G18)/SUM(EXP($E18)+EXP($F18)+EXP($G18))</f>
+        <v>0.40841911138939135</v>
+      </c>
+      <c r="L18" s="7">
+        <f ca="1">SUM(I18:K18)</f>
+        <v>1</v>
+      </c>
+      <c r="M18" s="7">
+        <f ca="1">-SUMPRODUCT(A18:C18, LN(I18:K18))</f>
+        <v>0.89546139802404756</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A19" s="64">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="B19" s="64">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C19" s="64">
+        <f t="shared" ref="C19:C27" ca="1" si="8">IF(SUM(A19:B19) &gt;0, 0, RANDBETWEEN(0,1))</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="64" t="str">
+        <f t="shared" ref="D19:D27" ca="1" si="9">IF(A19=1, "Cat", IF(B19=1, "Dog", "Fish"))</f>
+        <v>Cat</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" ref="E19:G27" ca="1" si="10">RAND()</f>
+        <v>0.99226561779035127</v>
+      </c>
+      <c r="F19" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.43527502078772784</v>
+      </c>
+      <c r="G19" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.89456754082227841</v>
+      </c>
+      <c r="H19" s="65" t="str">
+        <f t="shared" ref="H19:H27" ca="1" si="11">_xlfn.IFS(E19=MAX(E19:G19), "Cat", F19=MAX(E19:G19), "Dog", TRUE, "Fish")</f>
+        <v>Cat</v>
+      </c>
+      <c r="I19" s="3">
+        <f ca="1">EXP(E19)/SUM(EXP($E19)+EXP($F19)+EXP($G19))</f>
+        <v>0.40324965434974552</v>
+      </c>
+      <c r="J19" s="3">
+        <f ca="1">EXP(F19)/SUM(EXP($E19)+EXP($F19)+EXP($G19))</f>
+        <v>0.23103408710051937</v>
+      </c>
+      <c r="K19" s="3">
+        <f ca="1">EXP(G19)/SUM(EXP($E19)+EXP($F19)+EXP($G19))</f>
+        <v>0.36571625854973511</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" ref="L19:L27" ca="1" si="12">SUM(I19:K19)</f>
+        <v>1</v>
+      </c>
+      <c r="M19" s="7">
+        <f t="shared" ref="M19:M27" ca="1" si="13">-SUMPRODUCT(A19:C19, LN(I19:K19))</f>
+        <v>0.90819941913838764</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A20" s="64">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="B20" s="64">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="C20" s="64">
+        <f t="shared" ca="1" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D20" s="64" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>Dog</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.20981754538677522</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.79484812867656862</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.53181787211009612</v>
+      </c>
+      <c r="H20" s="65" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>Dog</v>
+      </c>
+      <c r="I20" s="3">
+        <f ca="1">EXP(E20)/SUM(EXP($E20)+EXP($F20)+EXP($G20))</f>
+        <v>0.23952491038789647</v>
+      </c>
+      <c r="J20" s="3">
+        <f ca="1">EXP(F20)/SUM(EXP($E20)+EXP($F20)+EXP($G20))</f>
+        <v>0.42995820431776471</v>
+      </c>
+      <c r="K20" s="3">
+        <f ca="1">EXP(G20)/SUM(EXP($E20)+EXP($F20)+EXP($G20))</f>
+        <v>0.33051688529433881</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" ca="1" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="M20" s="7">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.84406727427969552</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A21" s="64">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="B21" s="64">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C21" s="64">
+        <f t="shared" ca="1" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D21" s="64" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>Cat</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.56588822826886986</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.90290126404552751</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.73960427261820116</v>
+      </c>
+      <c r="H21" s="65" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>Dog</v>
+      </c>
+      <c r="I21" s="3">
+        <f ca="1">EXP(E21)/SUM(EXP($E21)+EXP($F21)+EXP($G21))</f>
+        <v>0.27851468009044511</v>
+      </c>
+      <c r="J21" s="3">
+        <f ca="1">EXP(F21)/SUM(EXP($E21)+EXP($F21)+EXP($G21))</f>
+        <v>0.39013147786099256</v>
+      </c>
+      <c r="K21" s="3">
+        <f ca="1">EXP(G21)/SUM(EXP($E21)+EXP($F21)+EXP($G21))</f>
+        <v>0.33135384204856239</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" ca="1" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="M21" s="7">
+        <f t="shared" ca="1" si="13"/>
+        <v>1.2782845097277047</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A22" s="64">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="B22" s="64">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="C22" s="64">
+        <f t="shared" ca="1" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D22" s="64" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>Dog</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.11197231619719028</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>9.5137711982993478E-2</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.21058797703470644</v>
+      </c>
+      <c r="H22" s="65" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>Fish</v>
+      </c>
+      <c r="I22" s="3">
+        <f ca="1">EXP(E22)/SUM(EXP($E22)+EXP($F22)+EXP($G22))</f>
+        <v>0.32394451939882196</v>
+      </c>
+      <c r="J22" s="3">
+        <f ca="1">EXP(F22)/SUM(EXP($E22)+EXP($F22)+EXP($G22))</f>
+        <v>0.31853668868830826</v>
+      </c>
+      <c r="K22" s="3">
+        <f ca="1">EXP(G22)/SUM(EXP($E22)+EXP($F22)+EXP($G22))</f>
+        <v>0.35751879191286984</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" ca="1" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="M22" s="7">
+        <f t="shared" ca="1" si="13"/>
+        <v>1.1440176184900235</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A23" s="64">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="B23" s="64">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C23" s="64">
+        <f t="shared" ca="1" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D23" s="64" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>Cat</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.20403883607759921</v>
+      </c>
+      <c r="F23" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.85599564831439134</v>
+      </c>
+      <c r="G23" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.24894168997210508</v>
+      </c>
+      <c r="H23" s="65" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>Dog</v>
+      </c>
+      <c r="I23" s="3">
+        <f ca="1">EXP(E23)/SUM(EXP($E23)+EXP($F23)+EXP($G23))</f>
+        <v>0.25219287378948674</v>
+      </c>
+      <c r="J23" s="3">
+        <f ca="1">EXP(F23)/SUM(EXP($E23)+EXP($F23)+EXP($G23))</f>
+        <v>0.48403198012914672</v>
+      </c>
+      <c r="K23" s="3">
+        <f ca="1">EXP(G23)/SUM(EXP($E23)+EXP($F23)+EXP($G23))</f>
+        <v>0.26377514608136648</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" ca="1" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="M23" s="7">
+        <f t="shared" ca="1" si="13"/>
+        <v>1.3775611120381337</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A24" s="64">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="B24" s="64">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C24" s="64">
+        <f t="shared" ca="1" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="64" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>Cat</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.52362872810635142</v>
+      </c>
+      <c r="F24" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>2.3259286730384354E-2</v>
+      </c>
+      <c r="G24" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.38957156459340048</v>
+      </c>
+      <c r="H24" s="65" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>Cat</v>
+      </c>
+      <c r="I24" s="3">
+        <f ca="1">EXP(E24)/SUM(EXP($E24)+EXP($F24)+EXP($G24))</f>
+        <v>0.40308818841071975</v>
+      </c>
+      <c r="J24" s="3">
+        <f ca="1">EXP(F24)/SUM(EXP($E24)+EXP($F24)+EXP($G24))</f>
+        <v>0.24439503851939565</v>
+      </c>
+      <c r="K24" s="3">
+        <f ca="1">EXP(G24)/SUM(EXP($E24)+EXP($F24)+EXP($G24))</f>
+        <v>0.35251677306988477</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" ca="1" si="12"/>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="M24" s="7">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.90859991117192829</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A25" s="64">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="B25" s="64">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C25" s="64">
+        <f t="shared" ca="1" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D25" s="64" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>Cat</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>8.7197000105152744E-2</v>
+      </c>
+      <c r="F25" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.11828478202524495</v>
+      </c>
+      <c r="G25" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.83417532553672513</v>
+      </c>
+      <c r="H25" s="65" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>Fish</v>
+      </c>
+      <c r="I25" s="3">
+        <f ca="1">EXP(E25)/SUM(EXP($E25)+EXP($F25)+EXP($G25))</f>
+        <v>0.24141825460188757</v>
+      </c>
+      <c r="J25" s="3">
+        <f ca="1">EXP(F25)/SUM(EXP($E25)+EXP($F25)+EXP($G25))</f>
+        <v>0.2490412903585964</v>
+      </c>
+      <c r="K25" s="3">
+        <f ca="1">EXP(G25)/SUM(EXP($E25)+EXP($F25)+EXP($G25))</f>
+        <v>0.50954045503951595</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="M25" s="7">
+        <f t="shared" ca="1" si="13"/>
+        <v>1.4212243534516042</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A26" s="64">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="B26" s="64">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C26" s="64">
+        <f t="shared" ca="1" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="64" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>Cat</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.68878440807752739</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.14706962355041753</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.26791923493298564</v>
+      </c>
+      <c r="H26" s="65" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>Cat</v>
+      </c>
+      <c r="I26" s="3">
+        <f ca="1">EXP(E26)/SUM(EXP($E26)+EXP($F26)+EXP($G26))</f>
+        <v>0.44678192260105648</v>
+      </c>
+      <c r="J26" s="3">
+        <f ca="1">EXP(F26)/SUM(EXP($E26)+EXP($F26)+EXP($G26))</f>
+        <v>0.2599153034900985</v>
+      </c>
+      <c r="K26" s="3">
+        <f ca="1">EXP(G26)/SUM(EXP($E26)+EXP($F26)+EXP($G26))</f>
+        <v>0.29330277390884496</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" ca="1" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="M26" s="7">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.80568467231676144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A27" s="64">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="B27" s="64">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C27" s="64">
+        <f t="shared" ca="1" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="64" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>Cat</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.48063928287652324</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.35156615831652582</v>
+      </c>
+      <c r="G27" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.52827373138022127</v>
+      </c>
+      <c r="H27" s="65" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>Fish</v>
+      </c>
+      <c r="I27" s="3">
+        <f ca="1">EXP(E27)/SUM(EXP($E27)+EXP($F27)+EXP($G27))</f>
+        <v>0.34156541356836173</v>
+      </c>
+      <c r="J27" s="3">
+        <f ca="1">EXP(F27)/SUM(EXP($E27)+EXP($F27)+EXP($G27))</f>
+        <v>0.30020515288503813</v>
+      </c>
+      <c r="K27" s="3">
+        <f ca="1">EXP(G27)/SUM(EXP($E27)+EXP($F27)+EXP($G27))</f>
+        <v>0.35822943354660003</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" ca="1" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="M27" s="7">
+        <f t="shared" ca="1" si="13"/>
+        <v>1.0742160705298587</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="33.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="74"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="63" t="s">
+        <v>38</v>
+      </c>
+      <c r="M28" s="67">
+        <f ca="1">SUM(M18:M27)</f>
+        <v>10.657316339168146</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="I16:K16"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04525B93-1571-4EE0-ACC9-EC2D13F2737E}">
   <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="15.25" defaultRowHeight="23.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="15.19921875" defaultRowHeight="23.4" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="25.25" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.19921875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.3984375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.8984375" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" style="2" customWidth="1"/>
     <col min="7" max="7" width="21.5" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5" style="2" customWidth="1"/>
     <col min="9" max="9" width="18" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="15.25" style="2"/>
+    <col min="10" max="10" width="28.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="15.19921875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="78" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="78" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="28" t="s">
+    <row r="2" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="54"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="30"/>
-    </row>
-    <row r="3" spans="1:10" ht="24" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="54"/>
+    </row>
+    <row r="3" spans="1:10" ht="24" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -1417,31 +2880,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="25.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="25.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <f ca="1">RANDBETWEEN(0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="3">
         <f ca="1">RAND()</f>
-        <v>0.76972992195186574</v>
+        <v>0.15261016612315559</v>
       </c>
       <c r="C4" s="6">
         <f ca="1">IF(B4&gt;= 0.5, TRUE, FALSE)*1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="7">
         <f ca="1">-A4*LN(B4)</f>
-        <v>0.26171557637368875</v>
+        <v>0</v>
       </c>
       <c r="E4" s="7">
         <f ca="1">-(1-A4)*LN(1-B4)</f>
-        <v>0</v>
+        <v>0.16559443770274968</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
         <f ca="1">RAND()</f>
-        <v>0.24170001993196877</v>
+        <v>6.4790673534059762E-3</v>
       </c>
       <c r="H4" s="6">
         <f ca="1">IF(G4&gt;= 0.5, TRUE, FALSE)*1</f>
@@ -1449,77 +2912,77 @@
       </c>
       <c r="I4" s="7">
         <f ca="1">-A4*LN(G4)</f>
-        <v>1.4200579088069656</v>
+        <v>0</v>
       </c>
       <c r="J4" s="7">
         <f ca="1">-(1-A4)*LN(1-G4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6.5001476132389539E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
         <f t="shared" ref="A5:A13" ca="1" si="0">RANDBETWEEN(0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" ref="B5:B13" ca="1" si="1">RAND()</f>
-        <v>0.60736590352902786</v>
+        <v>0.18011517426794244</v>
       </c>
       <c r="C5" s="6">
         <f t="shared" ref="C5:C13" ca="1" si="2">IF(B5&gt;= 0.5, TRUE, FALSE)*1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" ref="D5:D13" ca="1" si="3">-A5*LN(B5)</f>
-        <v>0.49862386306461554</v>
+        <v>0</v>
       </c>
       <c r="E5" s="7">
         <f t="shared" ref="E5:E13" ca="1" si="4">-(1-A5)*LN(1-B5)</f>
-        <v>0</v>
+        <v>0.19859140501308561</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G13" ca="1" si="5">RAND()</f>
-        <v>0.51921259700989886</v>
+        <v>0.11325184110207576</v>
       </c>
       <c r="H5" s="6">
         <f t="shared" ref="H5:H13" ca="1" si="6">IF(G5&gt;= 0.5, TRUE, FALSE)*1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="7">
         <f t="shared" ref="I5:I13" ca="1" si="7">-A5*LN(G5)</f>
-        <v>0.65544185154086076</v>
+        <v>0</v>
       </c>
       <c r="J5" s="7">
         <f t="shared" ref="J5:J13" ca="1" si="8">-(1-A5)*LN(1-G5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.12019426156633879</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89791942085216414</v>
+        <v>9.2668778870506729E-2</v>
       </c>
       <c r="C6" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>2.3787236606527595</v>
       </c>
       <c r="E6" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>2.2819927859315725</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>0.79694884338737215</v>
+        <v>0.65809299010565747</v>
       </c>
       <c r="H6" s="6">
         <f t="shared" ca="1" si="6"/>
@@ -1527,25 +2990,25 @@
       </c>
       <c r="I6" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>0.41840903529285878</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>1.5942973286699056</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="6">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.90816692198839621</v>
+        <v>0.45466715232140176</v>
       </c>
       <c r="C7" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" ca="1" si="3"/>
@@ -1553,16 +3016,16 @@
       </c>
       <c r="E7" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>2.3877827193340595</v>
+        <v>0.60635894105286858</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>0.38227974158616829</v>
+        <v>0.85379678171345486</v>
       </c>
       <c r="H7" s="6">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -1570,17 +3033,17 @@
       </c>
       <c r="J7" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>0.4817195802925287</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.9227577190048737</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.19324005868200278</v>
+        <v>0.12834241582227301</v>
       </c>
       <c r="C8" s="6">
         <f t="shared" ca="1" si="2"/>
@@ -1592,16 +3055,16 @@
       </c>
       <c r="E8" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>0.21472912545106254</v>
+        <v>0.13735861088689269</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>0.49638673680030077</v>
+        <v>0.7081218027602677</v>
       </c>
       <c r="H8" s="6">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -1609,17 +3072,17 @@
       </c>
       <c r="J8" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>0.68594664038413056</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.2314186964785609</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.18551853609768298</v>
+        <v>0.12186365371973795</v>
       </c>
       <c r="C9" s="6">
         <f t="shared" ca="1" si="2"/>
@@ -1631,12 +3094,12 @@
       </c>
       <c r="E9" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>0.20520360883887714</v>
+        <v>0.12995340551259887</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>0.34768890914869133</v>
+        <v>0.44184850562967526</v>
       </c>
       <c r="H9" s="6">
         <f t="shared" ca="1" si="6"/>
@@ -1648,34 +3111,34 @@
       </c>
       <c r="J9" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>0.42723369763980984</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.58312485816168202</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.41813158635891701</v>
+        <v>0.95870706076316514</v>
       </c>
       <c r="C10" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>0.87195909609475819</v>
+        <v>0</v>
       </c>
       <c r="E10" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>3.1870637564194557</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>0.57668228065123739</v>
+        <v>0.64480933295398013</v>
       </c>
       <c r="H10" s="6">
         <f t="shared" ca="1" si="6"/>
@@ -1683,21 +3146,21 @@
       </c>
       <c r="I10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>0.55046380425115571</v>
+        <v>0</v>
       </c>
       <c r="J10" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.0351005434175988</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77538668828217994</v>
+        <v>0.71614548913104337</v>
       </c>
       <c r="C11" s="6">
         <f t="shared" ca="1" si="2"/>
@@ -1705,7 +3168,7 @@
       </c>
       <c r="D11" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>0.25439342144209209</v>
+        <v>0.33387193555283234</v>
       </c>
       <c r="E11" s="7">
         <f t="shared" ca="1" si="4"/>
@@ -1714,37 +3177,37 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>2.1822637643092668E-2</v>
+        <v>0.71700652324899339</v>
       </c>
       <c r="H11" s="6">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>3.8248074239812517</v>
+        <v>0.33267034044762217</v>
       </c>
       <c r="J11" s="7">
         <f t="shared" ca="1" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83837880879690463</v>
+        <v>0.21861475799547447</v>
       </c>
       <c r="C12" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>0.17628524150184768</v>
+        <v>1.5204441941027806</v>
       </c>
       <c r="E12" s="7">
         <f t="shared" ca="1" si="4"/>
@@ -1753,37 +3216,37 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>0.8192496773564284</v>
+        <v>0.47159368835794946</v>
       </c>
       <c r="H12" s="6">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>0.1993663852312694</v>
+        <v>0.75163749387338841</v>
       </c>
       <c r="J12" s="7">
         <f t="shared" ca="1" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="25.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="8">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.69565027051868755</v>
+        <v>0.22848671409517129</v>
       </c>
       <c r="C13" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>0.36290822982249832</v>
+        <v>1.4762772143419325</v>
       </c>
       <c r="E13" s="7">
         <f t="shared" ca="1" si="4"/>
@@ -1792,7 +3255,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>0.56672609553969122</v>
+        <v>0.75444107790812409</v>
       </c>
       <c r="H13" s="6">
         <f t="shared" ca="1" si="6"/>
@@ -1800,36 +3263,36 @@
       </c>
       <c r="I13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>0.5678791686230753</v>
+        <v>0.28177809804757104</v>
       </c>
       <c r="J13" s="7">
         <f t="shared" ca="1" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10">
         <f ca="1">SUM(D4:D13)</f>
-        <v>2.4258854282995008</v>
+        <v>5.7093170046503046</v>
       </c>
       <c r="E14" s="11">
         <f ca="1">SUM(E4:E13)</f>
-        <v>5.0897082395555708</v>
+        <v>4.4249205565876508</v>
       </c>
       <c r="I14" s="12">
         <f ca="1">SUM(I4:I13)</f>
-        <v>7.2180165424345777</v>
+        <v>1.7844949676614403</v>
       </c>
       <c r="J14" s="11">
         <f ca="1">SUM(J4:J13)</f>
-        <v>3.1891972469863745</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="25.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>4.8990962262422935</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B15" s="13" t="s">
         <v>7</v>
       </c>
@@ -1837,27 +3300,27 @@
       <c r="D15" s="14"/>
       <c r="E15" s="15">
         <f ca="1">SUM(D14:E14)</f>
-        <v>7.5155936678550717</v>
+        <v>10.134237561237956</v>
       </c>
       <c r="I15" s="16"/>
       <c r="J15" s="15">
         <f ca="1">SUM(I14:J14)</f>
-        <v>10.407213789420952</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6.6835911939037338</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E17" s="17" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="17" t="str">
         <f ca="1">IF(E15&lt;= J15, "A", "B")</f>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G17" s="18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
@@ -1873,89 +3336,89 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D38A13D-2AB3-48AA-B828-ABDC8857A8FC}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultColWidth="13.5" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="13.5" defaultRowHeight="18" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="3" width="8.25" style="25" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="25" customWidth="1"/>
-    <col min="5" max="5" width="12.25" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.25" style="25" customWidth="1"/>
-    <col min="7" max="8" width="13.375" style="25" customWidth="1"/>
+    <col min="1" max="3" width="8.19921875" style="25" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" style="25" customWidth="1"/>
+    <col min="5" max="5" width="12.19921875" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.19921875" style="25" customWidth="1"/>
+    <col min="7" max="8" width="13.3984375" style="25" customWidth="1"/>
     <col min="9" max="9" width="14" style="25" customWidth="1"/>
-    <col min="10" max="10" width="15.25" style="25" customWidth="1"/>
-    <col min="11" max="11" width="3.75" style="25" customWidth="1"/>
-    <col min="12" max="12" width="16.375" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.125" style="25" customWidth="1"/>
+    <col min="10" max="10" width="15.19921875" style="25" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" style="25" customWidth="1"/>
+    <col min="12" max="12" width="16.3984375" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.09765625" style="25" customWidth="1"/>
     <col min="14" max="14" width="23.5" style="25" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="13.5" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="97.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="97.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="19" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
-      <c r="L1" s="32"/>
-    </row>
-    <row r="2" spans="1:14" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D2" s="49" t="s">
+      <c r="L1" s="28"/>
+    </row>
+    <row r="2" spans="1:14" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D2" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="49" t="s">
+      <c r="E2" s="57"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="50"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="56" t="s">
+      <c r="H2" s="57"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="L2" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="42"/>
-    </row>
-    <row r="3" spans="1:14" s="20" customFormat="1" ht="31.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="31" t="s">
+      <c r="M2" s="60"/>
+    </row>
+    <row r="3" spans="1:14" s="20" customFormat="1" ht="31.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="38" t="s">
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="G3" s="43" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="53" t="s">
+      <c r="I3" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="40" t="s">
+      <c r="J3" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="40"/>
-      <c r="L3" s="43" t="s">
+      <c r="K3" s="36"/>
+      <c r="L3" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="44" t="s">
+      <c r="M3" s="38" t="s">
         <v>20</v>
       </c>
       <c r="N3" s="21"/>
     </row>
-    <row r="4" spans="1:14" s="20" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" s="20" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="22">
         <f ca="1">RANDBETWEEN(0,1)</f>
         <v>1</v>
@@ -1968,46 +3431,46 @@
         <f ca="1">IF(SUM(A4:B4) &gt;0, 0, RANDBETWEEN(0,1))</f>
         <v>0</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="30">
         <f ca="1">RAND()</f>
-        <v>0.26370820105935566</v>
-      </c>
-      <c r="E4" s="33">
+        <v>0.68248507899260713</v>
+      </c>
+      <c r="E4" s="29">
         <f t="shared" ref="E4:F4" ca="1" si="0">RAND()</f>
-        <v>0.72360090081097161</v>
-      </c>
-      <c r="F4" s="33">
+        <v>6.9449508051247055E-2</v>
+      </c>
+      <c r="F4" s="29">
         <f t="shared" ca="1" si="0"/>
-        <v>0.1734885069573765</v>
-      </c>
-      <c r="G4" s="54">
+        <v>0.38824228601057298</v>
+      </c>
+      <c r="G4" s="45">
         <f ca="1">EXP(D4)/SUM(EXP($D4)+EXP($E4)+EXP($F4))</f>
-        <v>0.28590752288007315</v>
+        <v>0.43729237119293735</v>
       </c>
       <c r="H4" s="21">
         <f t="shared" ref="H4:I4" ca="1" si="1">EXP(E4)/SUM(EXP($D4)+EXP($E4)+EXP($F4))</f>
-        <v>0.45285007557594592</v>
-      </c>
-      <c r="I4" s="55">
+        <v>0.2368830222015342</v>
+      </c>
+      <c r="I4" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>0.26124240154398087</v>
+        <v>0.32582460660552859</v>
       </c>
       <c r="J4" s="23">
         <f ca="1">SUM(G4:I4)</f>
         <v>1</v>
       </c>
       <c r="K4" s="23"/>
-      <c r="L4" s="45">
+      <c r="L4" s="39">
         <f ca="1">-(A4*LN(G4) + B4*LN(H4) + C4*LN(I4))</f>
-        <v>1.2520868670232301</v>
-      </c>
-      <c r="M4" s="46">
+        <v>0.82715326596368899</v>
+      </c>
+      <c r="M4" s="40">
         <f ca="1">-SUMPRODUCT(A4:C4, LN(G4:I4))</f>
-        <v>1.2520868670232301</v>
+        <v>0.82715326596368899</v>
       </c>
       <c r="N4" s="23"/>
     </row>
-    <row r="5" spans="1:14" s="20" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" s="20" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="22">
         <f t="shared" ref="A5:A13" ca="1" si="2">RANDBETWEEN(0,1)</f>
         <v>1</v>
@@ -2020,46 +3483,46 @@
         <f t="shared" ref="C5" ca="1" si="4">IF(SUM(A5:B5) &gt;0, 0, RANDBETWEEN(0,1))</f>
         <v>0</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="30">
         <f t="shared" ref="D5:F13" ca="1" si="5">RAND()</f>
-        <v>0.23295965581404054</v>
-      </c>
-      <c r="E5" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.37892674164166051</v>
-      </c>
-      <c r="F5" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.95423402634406818</v>
-      </c>
-      <c r="G5" s="54">
-        <f t="shared" ref="G5:G13" ca="1" si="6">EXP(D5)/SUM(EXP($D5)+EXP($E5)+EXP($F5))</f>
-        <v>0.23729233748026804</v>
+        <v>0.77920918517425553</v>
+      </c>
+      <c r="E5" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.8035368169477185</v>
+      </c>
+      <c r="F5" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.22549136018094251</v>
+      </c>
+      <c r="G5" s="45">
+        <f t="shared" ref="G5:G12" ca="1" si="6">EXP(D5)/SUM(EXP($D5)+EXP($E5)+EXP($F5))</f>
+        <v>0.38469901858032174</v>
       </c>
       <c r="H5" s="21">
         <f t="shared" ref="H5:H13" ca="1" si="7">EXP(E5)/SUM(EXP($D5)+EXP($E5)+EXP($F5))</f>
-        <v>0.27458475050728176</v>
-      </c>
-      <c r="I5" s="55">
+        <v>0.39417260234916446</v>
+      </c>
+      <c r="I5" s="46">
         <f t="shared" ref="I5:I13" ca="1" si="8">EXP(F5)/SUM(EXP($D5)+EXP($E5)+EXP($F5))</f>
-        <v>0.48812291201245017</v>
+        <v>0.22112837907051378</v>
       </c>
       <c r="J5" s="23">
         <f t="shared" ref="J5:J13" ca="1" si="9">SUM(G5:I5)</f>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="K5" s="23"/>
-      <c r="L5" s="45">
+      <c r="L5" s="39">
         <f t="shared" ref="L5:L13" ca="1" si="10">-(A5*LN(G5) + B5*LN(H5) + C5*LN(I5))</f>
-        <v>1.4384624064946867</v>
-      </c>
-      <c r="M5" s="46" cm="1">
+        <v>0.95529402035705668</v>
+      </c>
+      <c r="M5" s="40" cm="1">
         <f t="array" aca="1" ref="M5" ca="1">-SUMPRODUCT(A5:C5, LN(G5:I5))</f>
-        <v>1.4384624064946867</v>
+        <v>0.95529402035705668</v>
       </c>
       <c r="N5" s="23"/>
     </row>
-    <row r="6" spans="1:14" s="20" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" s="20" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="22">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
@@ -2071,49 +3534,49 @@
         <f t="shared" ref="C6:C13" ca="1" si="11">IF(SUM(A6:B6) &gt;0, 0, RANDBETWEEN(0,1))</f>
         <v>0</v>
       </c>
-      <c r="D6" s="34">
-        <f t="shared" ca="1" si="5"/>
-        <v>8.8212247359789941E-2</v>
-      </c>
-      <c r="E6" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.49330972604937418</v>
-      </c>
-      <c r="F6" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.11205510872882707</v>
-      </c>
-      <c r="G6" s="54">
+      <c r="D6" s="30">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.43230825134560513</v>
+      </c>
+      <c r="E6" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.80649889585783918</v>
+      </c>
+      <c r="F6" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.29887815965395625</v>
+      </c>
+      <c r="G6" s="45">
         <f t="shared" ca="1" si="6"/>
-        <v>0.28380242777850251</v>
+        <v>0.30039926710404474</v>
       </c>
       <c r="H6" s="21">
         <f t="shared" ca="1" si="7"/>
-        <v>0.42554716924917452</v>
-      </c>
-      <c r="I6" s="55">
+        <v>0.43672474594596333</v>
+      </c>
+      <c r="I6" s="46">
         <f t="shared" ca="1" si="8"/>
-        <v>0.29065040297232297</v>
+        <v>0.26287598694999204</v>
       </c>
       <c r="J6" s="23">
         <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="K6" s="23"/>
-      <c r="L6" s="45">
+      <c r="L6" s="39">
         <f t="shared" ca="1" si="10"/>
-        <v>0.85437948106302219</v>
-      </c>
-      <c r="M6" s="46">
-        <f t="shared" ref="M5:M13" ca="1" si="12">-SUMPRODUCT(A6:C6, LN(G6:I6))</f>
-        <v>0.85437948106302219</v>
+        <v>0.82845215431643893</v>
+      </c>
+      <c r="M6" s="40">
+        <f t="shared" ref="M6:M13" ca="1" si="12">-SUMPRODUCT(A6:C6, LN(G6:I6))</f>
+        <v>0.82845215431643893</v>
       </c>
       <c r="N6" s="23"/>
     </row>
-    <row r="7" spans="1:14" s="20" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" s="20" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="22">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" s="22">
         <f t="shared" ca="1" si="3"/>
@@ -2123,101 +3586,101 @@
         <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
-      <c r="D7" s="34">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.69314374736755779</v>
-      </c>
-      <c r="E7" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.36835859047143671</v>
-      </c>
-      <c r="F7" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.46819885636636416</v>
-      </c>
-      <c r="G7" s="54">
+      <c r="D7" s="30">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.25882323326061785</v>
+      </c>
+      <c r="E7" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.50810990942379863</v>
+      </c>
+      <c r="F7" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.72584792921460795</v>
+      </c>
+      <c r="G7" s="45">
         <f t="shared" ca="1" si="6"/>
-        <v>0.3966297850374364</v>
+        <v>0.25784156692902394</v>
       </c>
       <c r="H7" s="21">
         <f t="shared" ca="1" si="7"/>
-        <v>0.28663744442220174</v>
-      </c>
-      <c r="I7" s="55">
+        <v>0.33083904584732543</v>
+      </c>
+      <c r="I7" s="46">
         <f t="shared" ca="1" si="8"/>
-        <v>0.31673277054036175</v>
+        <v>0.41131938722365069</v>
       </c>
       <c r="J7" s="23">
         <f t="shared" ca="1" si="9"/>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="K7" s="23"/>
-      <c r="L7" s="45">
+      <c r="L7" s="39">
         <f t="shared" ca="1" si="10"/>
-        <v>0.92475196476469645</v>
-      </c>
-      <c r="M7" s="46">
+        <v>0</v>
+      </c>
+      <c r="M7" s="40">
         <f t="shared" ca="1" si="12"/>
-        <v>0.92475196476469645</v>
+        <v>0</v>
       </c>
       <c r="N7" s="23"/>
     </row>
-    <row r="8" spans="1:14" s="20" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" s="20" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="22">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="22">
         <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
-      <c r="D8" s="34">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.67141135701926424</v>
-      </c>
-      <c r="E8" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.35552649824381743</v>
-      </c>
-      <c r="F8" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>7.0576734261572627E-3</v>
-      </c>
-      <c r="G8" s="54">
+      <c r="D8" s="30">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.34771342458224763</v>
+      </c>
+      <c r="E8" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>1.1182671728297455E-2</v>
+      </c>
+      <c r="F8" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.66770470428809081</v>
+      </c>
+      <c r="G8" s="45">
         <f t="shared" ca="1" si="6"/>
-        <v>0.44568256678647616</v>
+        <v>0.32348225556885929</v>
       </c>
       <c r="H8" s="21">
         <f t="shared" ca="1" si="7"/>
-        <v>0.32496650197758076</v>
-      </c>
-      <c r="I8" s="55">
+        <v>0.23104523368551502</v>
+      </c>
+      <c r="I8" s="46">
         <f t="shared" ca="1" si="8"/>
-        <v>0.22935093123594297</v>
+        <v>0.44547251074562572</v>
       </c>
       <c r="J8" s="23">
         <f t="shared" ca="1" si="9"/>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="K8" s="23"/>
-      <c r="L8" s="45">
+      <c r="L8" s="39">
         <f t="shared" ca="1" si="10"/>
-        <v>0.80814831402732967</v>
-      </c>
-      <c r="M8" s="46">
+        <v>1.4651417708095433</v>
+      </c>
+      <c r="M8" s="40">
         <f t="shared" ca="1" si="12"/>
-        <v>0.80814831402732967</v>
+        <v>1.4651417708095433</v>
       </c>
       <c r="N8" s="23"/>
     </row>
-    <row r="9" spans="1:14" s="20" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" s="20" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="22">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" s="22">
         <f t="shared" ca="1" si="3"/>
@@ -2227,153 +3690,153 @@
         <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
-      <c r="D9" s="34">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.37087044312104922</v>
-      </c>
-      <c r="E9" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.23105443266629311</v>
-      </c>
-      <c r="F9" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.60718202801777754</v>
-      </c>
-      <c r="G9" s="54">
+      <c r="D9" s="30">
+        <f t="shared" ca="1" si="5"/>
+        <v>2.5100950815192813E-2</v>
+      </c>
+      <c r="E9" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.14041579884401456</v>
+      </c>
+      <c r="F9" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.15006928867025848</v>
+      </c>
+      <c r="G9" s="45">
         <f t="shared" ca="1" si="6"/>
-        <v>0.31886869515729088</v>
+        <v>0.30718764201261867</v>
       </c>
       <c r="H9" s="21">
         <f t="shared" ca="1" si="7"/>
-        <v>0.27726213478728273</v>
-      </c>
-      <c r="I9" s="55">
+        <v>0.34473417771580322</v>
+      </c>
+      <c r="I9" s="46">
         <f t="shared" ca="1" si="8"/>
-        <v>0.40386917005542633</v>
+        <v>0.34807818027157811</v>
       </c>
       <c r="J9" s="23">
         <f t="shared" ca="1" si="9"/>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="K9" s="23"/>
-      <c r="L9" s="45">
+      <c r="L9" s="39">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="46">
+        <v>1.1802965063412876</v>
+      </c>
+      <c r="M9" s="40">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>1.1802965063412876</v>
       </c>
       <c r="N9" s="23"/>
     </row>
-    <row r="10" spans="1:14" s="20" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" s="20" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="22">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="B10" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="22">
         <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
-      <c r="D10" s="34">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.79724610632314408</v>
-      </c>
-      <c r="E10" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.54104641844007917</v>
-      </c>
-      <c r="F10" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.57305434397621857</v>
-      </c>
-      <c r="G10" s="54">
+      <c r="D10" s="30">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.96632258174273544</v>
+      </c>
+      <c r="E10" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.84213375431094262</v>
+      </c>
+      <c r="F10" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.73551673288043229</v>
+      </c>
+      <c r="G10" s="45">
         <f t="shared" ca="1" si="6"/>
-        <v>0.38862883410859561</v>
+        <v>0.37353760447605422</v>
       </c>
       <c r="H10" s="21">
         <f t="shared" ca="1" si="7"/>
-        <v>0.30079381988761822</v>
-      </c>
-      <c r="I10" s="55">
+        <v>0.32991328704504252</v>
+      </c>
+      <c r="I10" s="46">
         <f t="shared" ca="1" si="8"/>
-        <v>0.31057734600378623</v>
+        <v>0.29654910847890331</v>
       </c>
       <c r="J10" s="23">
         <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="45">
+      <c r="L10" s="39">
         <f t="shared" ca="1" si="10"/>
-        <v>1.2013302327038913</v>
-      </c>
-      <c r="M10" s="46">
+        <v>0</v>
+      </c>
+      <c r="M10" s="40">
         <f t="shared" ca="1" si="12"/>
-        <v>1.2013302327038913</v>
+        <v>0</v>
       </c>
       <c r="N10" s="23"/>
     </row>
-    <row r="11" spans="1:14" s="20" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" s="20" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="22">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="22">
         <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
-      <c r="D11" s="34">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.63648686212261152</v>
-      </c>
-      <c r="E11" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.5622053096337265</v>
-      </c>
-      <c r="F11" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.42492598511395163</v>
-      </c>
-      <c r="G11" s="54">
+      <c r="D11" s="30">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.60839711934337348</v>
+      </c>
+      <c r="E11" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.2965327957622661</v>
+      </c>
+      <c r="F11" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.91949647776218568</v>
+      </c>
+      <c r="G11" s="45">
         <f t="shared" ca="1" si="6"/>
-        <v>0.36526607841893649</v>
+        <v>0.32289253030395015</v>
       </c>
       <c r="H11" s="21">
         <f t="shared" ca="1" si="7"/>
-        <v>0.33911677513355587</v>
-      </c>
-      <c r="I11" s="55">
+        <v>0.23638343726806077</v>
+      </c>
+      <c r="I11" s="46">
         <f t="shared" ca="1" si="8"/>
-        <v>0.29561714644750769</v>
+        <v>0.44072403242798891</v>
       </c>
       <c r="J11" s="23">
         <f t="shared" ca="1" si="9"/>
-        <v>1</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="K11" s="23"/>
-      <c r="L11" s="45">
+      <c r="L11" s="39">
         <f t="shared" ca="1" si="10"/>
-        <v>1.0814107614971376</v>
-      </c>
-      <c r="M11" s="46">
+        <v>1.1304357346414133</v>
+      </c>
+      <c r="M11" s="40">
         <f t="shared" ca="1" si="12"/>
-        <v>1.0814107614971376</v>
+        <v>1.1304357346414133</v>
       </c>
       <c r="N11" s="23"/>
     </row>
-    <row r="12" spans="1:14" s="20" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" s="20" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="22">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12" s="22">
         <f t="shared" ca="1" si="3"/>
@@ -2381,116 +3844,116 @@
       </c>
       <c r="C12" s="22">
         <f t="shared" ca="1" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="D12" s="34">
-        <f t="shared" ca="1" si="5"/>
-        <v>6.9600460890463123E-2</v>
-      </c>
-      <c r="E12" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.97791275778413433</v>
-      </c>
-      <c r="F12" s="33">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.96216835199930928</v>
-      </c>
-      <c r="G12" s="54">
+        <v>0</v>
+      </c>
+      <c r="D12" s="30">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.35471764276890072</v>
+      </c>
+      <c r="E12" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.40980822788472571</v>
+      </c>
+      <c r="F12" s="29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.51825021302843077</v>
+      </c>
+      <c r="G12" s="45">
         <f t="shared" ca="1" si="6"/>
-        <v>0.1688754418996988</v>
+        <v>0.30918590992979961</v>
       </c>
       <c r="H12" s="21">
         <f t="shared" ca="1" si="7"/>
-        <v>0.41883360204919606</v>
-      </c>
-      <c r="I12" s="55">
+        <v>0.32669706387726094</v>
+      </c>
+      <c r="I12" s="46">
         <f t="shared" ca="1" si="8"/>
-        <v>0.41229095605110516</v>
+        <v>0.36411702619293945</v>
       </c>
       <c r="J12" s="23">
         <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="K12" s="23"/>
-      <c r="L12" s="45">
+      <c r="L12" s="39">
         <f ca="1">-(A12*LN(G12) + B12*LN(H12) + C12*LN(I12))</f>
-        <v>0.88602597486978585</v>
-      </c>
-      <c r="M12" s="46">
+        <v>1.1738125327450941</v>
+      </c>
+      <c r="M12" s="40">
         <f t="shared" ca="1" si="12"/>
-        <v>0.88602597486978585</v>
+        <v>1.1738125327450941</v>
       </c>
       <c r="N12" s="23"/>
     </row>
-    <row r="13" spans="1:14" s="20" customFormat="1" ht="25.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="57">
+    <row r="13" spans="1:14" s="20" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="48">
         <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
-      <c r="B13" s="57">
+      <c r="B13" s="48">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="C13" s="57">
+      <c r="C13" s="48">
         <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
-      <c r="D13" s="58">
-        <f t="shared" ca="1" si="5"/>
-        <v>4.3356945652884171E-2</v>
-      </c>
-      <c r="E13" s="59">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.84732269731156495</v>
-      </c>
-      <c r="F13" s="59">
-        <f t="shared" ca="1" si="5"/>
-        <v>3.8453721185025769E-2</v>
-      </c>
-      <c r="G13" s="43">
+      <c r="D13" s="49">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.3891204584883039</v>
+      </c>
+      <c r="E13" s="50">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.9325898875493599</v>
+      </c>
+      <c r="F13" s="50">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.84498127831781655</v>
+      </c>
+      <c r="G13" s="37">
         <f ca="1">EXP(D13)/SUM(EXP($D13)+EXP($E13)+EXP($F13))</f>
-        <v>0.23643494844284083</v>
-      </c>
-      <c r="H13" s="40">
+        <v>0.23258510131719792</v>
+      </c>
+      <c r="H13" s="36">
         <f t="shared" ca="1" si="7"/>
-        <v>0.52828655923967394</v>
-      </c>
-      <c r="I13" s="44">
+        <v>0.40050474506367634</v>
+      </c>
+      <c r="I13" s="38">
         <f t="shared" ca="1" si="8"/>
-        <v>0.23527849231748535</v>
-      </c>
-      <c r="J13" s="60">
+        <v>0.36691015361912588</v>
+      </c>
+      <c r="J13" s="51">
         <f t="shared" ca="1" si="9"/>
         <v>1.0000000000000002</v>
       </c>
-      <c r="K13" s="60"/>
-      <c r="L13" s="47">
+      <c r="K13" s="51"/>
+      <c r="L13" s="41">
         <f t="shared" ca="1" si="10"/>
-        <v>1.4420821683242402</v>
-      </c>
-      <c r="M13" s="48">
+        <v>1.4584990937555853</v>
+      </c>
+      <c r="M13" s="42">
         <f t="shared" ca="1" si="12"/>
-        <v>1.4420821683242402</v>
+        <v>1.4584990937555853</v>
       </c>
       <c r="N13" s="23"/>
     </row>
-    <row r="14" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J14" s="35"/>
-      <c r="K14" s="36" t="s">
+    <row r="14" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J14" s="31"/>
+      <c r="K14" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="33">
         <f ca="1">SUM(L4:L13)</f>
-        <v>9.8886781707680207</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9.0190850789301074</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="J15" s="26"/>
       <c r="K15" s="26"/>
       <c r="L15" s="26"/>
     </row>
-    <row r="17" spans="4:4" ht="34.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D18" s="25" t="s">
         <v>12</v>
       </c>
